--- a/data/trans_dic/P25C$smedicoempresa_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P25C$smedicoempresa_2023-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo método para dejar de fumar fue, al menos, la ayuda del médico de empresa</t>
+          <t>Población cuyo método para dejar de fumar fue, al menos, la ayuda del médico de empresa (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,09</t>
+          <t>0,0; 2,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,37</t>
+          <t>0,0; 1,34</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,34</t>
+          <t>0,0; 1,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,62</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,89</t>
+          <t>0,0; 0,95</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,17</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,62</t>
+          <t>0,0; 2,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,97</t>
+          <t>0,0; 0,86</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,85</t>
+          <t>0,0; 0,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,57</t>
+          <t>0,0; 0,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,65</t>
+          <t>0,04; 0,63</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo método para dejar de fumar fue, al menos, la ayuda del médico de empresa</t>
+          <t>Población cuyo método para dejar de fumar fue, al menos, la ayuda del médico de empresa (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3461</t>
+          <t>0; 3355</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 1132</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2872</t>
+          <t>0; 2819</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 7294</t>
+          <t>0; 7240</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 1258</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 6671</t>
+          <t>0; 7088</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 1606</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2282</t>
+          <t>0; 1795</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 2168</t>
+          <t>0; 1925</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>354; 7225</t>
+          <t>0; 7237</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 1900</t>
+          <t>0; 2318</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>637; 7688</t>
+          <t>514; 7498</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25C$smedicoempresa_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P25C$smedicoempresa_2023-Estudios-trans_dic.xlsx
@@ -549,7 +549,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -559,7 +559,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,02</t>
+          <t>0,0; 1,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,34</t>
+          <t>0,0; 1,43</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,31%</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,33</t>
+          <t>0,0; 1,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,95</t>
+          <t>0,0; 1,12</t>
         </is>
       </c>
     </row>
@@ -654,12 +654,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,06</t>
+          <t>0,0; 1,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,86</t>
+          <t>0,0; 0,81</t>
         </is>
       </c>
     </row>
@@ -699,7 +699,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,26%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,85</t>
+          <t>0,09; 1,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,69</t>
+          <t>0,0; 0,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,63</t>
+          <t>0,08; 0,73</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>571</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>571</t>
         </is>
       </c>
     </row>
@@ -879,7 +879,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3355</t>
+          <t>0; 2868</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2819</t>
+          <t>0; 3183</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1771</t>
+          <t>1708</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1771</t>
+          <t>1708</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 7240</t>
+          <t>0; 6074</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 7088</t>
+          <t>0; 6206</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>389</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>389</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 1795</t>
+          <t>0; 1667</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 1925</t>
+          <t>0; 1984</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2331</t>
+          <t>2279</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>389</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2708</t>
+          <t>2668</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 7237</t>
+          <t>572; 6678</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 2318</t>
+          <t>0; 2301</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>514; 7498</t>
+          <t>772; 7461</t>
         </is>
       </c>
     </row>
